--- a/data/roadmap/Neurodivergent_map.xlsx
+++ b/data/roadmap/Neurodivergent_map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
   <si>
     <t xml:space="preserve">Neurodivergent Path - Domain to Modality</t>
   </si>
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Relevance</t>
   </si>
   <si>
-    <t xml:space="preserve">A. Sensory Processing</t>
+    <t xml:space="preserve">A. Sensory Processing , Body Awareness &amp; Skills ,   Motor Planning &amp; Coordination</t>
   </si>
   <si>
     <t xml:space="preserve">Spine</t>
@@ -64,7 +64,27 @@
     <t xml:space="preserve">Safe and Sound Protocol (SSP)</t>
   </si>
   <si>
-    <t xml:space="preserve">C. Cognitive Function</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF33312E"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C. Cognitive Function , </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF33312E"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Academic &amp; Learning</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Arrowsmith</t>
@@ -73,16 +93,7 @@
     <t xml:space="preserve">Stowell</t>
   </si>
   <si>
-    <t xml:space="preserve">D. Academic &amp; Learning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E. Motor Planning &amp; Coordination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F. Body Awareness &amp; Skills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G. Behaviour &amp; Self-Regulation</t>
+    <t xml:space="preserve">D. Behaviour &amp; Self-Regulation , Social Interaction &amp; Communication</t>
   </si>
   <si>
     <t xml:space="preserve">Complementary</t>
@@ -94,10 +105,10 @@
     <t xml:space="preserve">Yoga Nidra</t>
   </si>
   <si>
-    <t xml:space="preserve">H. Emotional Regulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J. General Health &amp; Foundations</t>
+    <t xml:space="preserve">E. Emotional Regulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F. General Health &amp; Foundations, Gut Health</t>
   </si>
   <si>
     <t xml:space="preserve">Nemechek Protocol</t>
@@ -110,7 +121,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,6 +196,13 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF33312E"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -303,72 +321,68 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -621,306 +635,232 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D1048576"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="7" t="s">
+    <row r="6" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="7" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="7" t="s">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>8</v>
+      <c r="B11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="8" t="s">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="5" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="D16" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="14" t="s">
+      <c r="D20" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-    </row>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
@@ -928,19 +868,13 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="A22:D22"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
